--- a/App Data.xlsx
+++ b/App Data.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1146,10 +1146,30 @@
         <v>each</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>60501</v>
+      </c>
+      <c r="B38" t="str">
+        <v>9 Paper Plates - 12x100</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Packaging</v>
+      </c>
+      <c r="D38" t="str">
+        <v>12x100</v>
+      </c>
+      <c r="E38">
+        <v>1200</v>
+      </c>
+      <c r="F38" t="str">
+        <v>each</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F38"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/App Data.xlsx
+++ b/App Data.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1166,10 +1166,30 @@
         <v>each</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>G060510</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Ginos Pizza Slice Tray - 500/cs</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Packaging</v>
+      </c>
+      <c r="D39" t="str">
+        <v>500/cs</v>
+      </c>
+      <c r="E39">
+        <v>500</v>
+      </c>
+      <c r="F39" t="str">
+        <v>each</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F39"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/App Data.xlsx
+++ b/App Data.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F43"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1186,10 +1186,90 @@
         <v>each</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>P1250</v>
+      </c>
+      <c r="B40" t="str">
+        <v>CRUSHED TOMATOES &amp; SPICE - CASE 6/100 ML</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Pizza Sauce</v>
+      </c>
+      <c r="D40" t="str">
+        <v>6x100oz</v>
+      </c>
+      <c r="E40">
+        <v>600</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Fl oz</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>P1352</v>
+      </c>
+      <c r="B41" t="str">
+        <v>SLICE DOUGH - CASE OF 14/32oz</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Dough</v>
+      </c>
+      <c r="D41" t="str">
+        <v>14x32oz</v>
+      </c>
+      <c r="E41">
+        <v>12.7</v>
+      </c>
+      <c r="F41" t="str">
+        <v>kg</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>50125</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Whole Wheat Dough L 36 x550 grms</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Dough</v>
+      </c>
+      <c r="D42" t="str">
+        <v>36x550g</v>
+      </c>
+      <c r="E42">
+        <v>19.8</v>
+      </c>
+      <c r="F42" t="str">
+        <v>kg</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>20102</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Cheese -10KG IQF</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Cheese</v>
+      </c>
+      <c r="D43" t="str">
+        <v>10kg</v>
+      </c>
+      <c r="E43">
+        <v>10</v>
+      </c>
+      <c r="F43" t="str">
+        <v>kg</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F43"/>
   </ignoredErrors>
 </worksheet>
 </file>
